--- a/www/download/COUNTRY.IDN.WIOD16.xlsx
+++ b/www/download/COUNTRY.IDN.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Indonésia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>8356.52264272572</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>10201.6977793222</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>9285.30974000918</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>8580.81841431976</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>8927.85392901545</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>9694.43147181627</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>9158.43171086464</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>9138.3453643482</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>9630.84945106642</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>10324.5202890591</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>9088.43042860905</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>8765.85522362486</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>9381.83114052943</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>10394.3296646812</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>11857.1919576017</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>96.875</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>99.381</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>100.23</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>103.735</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>104.667</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>106.265</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>108.611</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>113.379</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>115.174</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>117.182</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>121.658</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>123.606</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>135.569</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>151.171</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>168.804</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>36.469</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>40.516</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>40.597</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>39.526</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.854</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>43.155</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>44.873</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>46.55</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>47.214</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>52.063</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>53.991</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>59.919</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>66.912</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>74.641</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>159660.176</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>165538.318</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>176488.77</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>185008.412</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>194145.927</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>166608.509</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>155857.243</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>157350.939</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>159747.607</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>162810.544</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>169976.613</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>173429.409</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>190651.007</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>212782.301</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>237573.657</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>68936.963</t>
+          <t>162117655841.498</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>74522.705</t>
+          <t>170020213123.887</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78386.638</t>
+          <t>182916486463.042</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>77871.127</t>
+          <t>200679102953.581</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>82806.33</t>
+          <t>199580378943.182</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>72426.913</t>
+          <t>178749919108.338</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>68493.533</t>
+          <t>176793910295.378</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>68041.404</t>
+          <t>183237100821.146</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>68774.789</t>
+          <t>187697954678.573</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>70833.183</t>
+          <t>196659371129.233</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>76726.992</t>
+          <t>200039787796.104</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>80070.701</t>
+          <t>201134169241.38</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>89154.68</t>
+          <t>218263615876.686</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>99676.829</t>
+          <t>238070935317.153</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>111104.239</t>
+          <t>262828496222.359</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>28611423056.2854</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30544630510.3717</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>31217828095.0702</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>36250532693.5276</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>37034443788.5825</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>34797518518.4153</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>33163348597.8868</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>33999857600.7279</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>33260404381.6169</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>36182746238.1147</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>37112772635.4446</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>37747551478.6751</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>40594814052.9312</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>43946760039.3078</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>48668955744.7654</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>18816168.5775337</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19711772.4355582</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>17398399.0379062</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>15797183.1800073</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>14891367.0562952</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>12818390.721359</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>9778843.10530713</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>8359588.65706695</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7162635.20883658</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6994718.69921105</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>5710356.10350451</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4963672.07753986</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>5240540.31658692</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5698698.41713506</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>6388236.70959166</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>834829.995590035</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>869770.257822491</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>922718.509098942</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1061799.35710637</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1187247.76292397</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1157416.40415052</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1138890.50067918</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1316241.6548182</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1438157.1828379</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1325464.16300773</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1524196.54558201</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1615249.808886</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1732915.49925615</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1929466.3139959</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2159883.59673246</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1317265.31560639</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1368491.62499289</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1481130.36124513</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1768438.37390889</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1944444.69874403</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1869810.14025494</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1953716.96002463</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2286266.74609433</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2541925.91180378</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2423684.16507267</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2731311.59681978</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2916429.98037989</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3083628.54968509</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3360123.26992706</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3726734.4342725</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.40942098071756</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.43979723292757</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.51095744909872</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.14813745382295</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.23592746451693</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.0813815491375</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.06533826937984</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.00122614626902</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1.06776767386544</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.957650824341928</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.06740123551755</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.12121575740442</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.19620860644298</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.26812690880613</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.28285643897239</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>47009.63222317</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>43052.9773144481</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>47889.7629920168</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>56760.1890529227</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>68309.9685858849</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>72825.1028524078</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>93682.5308605352</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>108785.841892878</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>131244.700206299</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>131661.531588079</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>163862.076092308</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>191610.308481603</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>203278.245823974</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>192662.43029874</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>188264.133290177</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8356.52264272572</t>
+          <t>784.535892809961</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10201.6977793222</t>
+          <t>753.888750845941</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9285.30974000918</t>
+          <t>768.966493662709</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8580.81841431976</t>
+          <t>917.128446329005</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8927.85392901545</t>
+          <t>906.499910978402</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>9694.43147181627</t>
+          <t>806.330706301651</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>9158.43171086464</t>
+          <t>739.054464995683</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>9138.3453643482</t>
+          <t>730.392825397014</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>9630.84945106642</t>
+          <t>704.456531030433</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>10324.5202890591</t>
+          <t>746.350934226466</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>9088.43042860905</t>
+          <t>712.837463235857</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>8765.85522362486</t>
+          <t>699.148324291603</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>9381.83114052943</t>
+          <t>677.500426586584</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>10394.3296646812</t>
+          <t>656.787682867509</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>11857.1919576017</t>
+          <t>652.041375341455</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>-13842966289.0305</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>-13313029316.5579</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-9885821442.55886</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>-9805691754.00214</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>-10247871428.1492</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>-9023386944.37717</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>-4103307455.77147</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>-4788227560.71738</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>-5439645308.16158</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>-3593498748.12123</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>-1780425730.3057</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>1393671534.93515</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-366784238.89832</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-2589225305.79631</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>-6234597618.23405</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-13246373989.1771</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>-12858251397.5605</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>-9463773213.2362</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>-9565653684.40099</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>-10102795082.416</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>-8322338144.85834</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>-3436529343.59542</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-4194138574.08738</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>-5140848564.41008</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-3252314625.60989</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>-1314387125.99846</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>1914716181.19845</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>-451421.539792689</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-2105402648.29666</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>-5841260731.56488</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-596592299.853367</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>-454777918.997385</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>-422048229.322666</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>-240038069.601153</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>-145076345.733207</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>-701048799.518831</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-666778112.176052</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>-594088986.629995</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>-298796743.751499</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.816</t>
+          <t>-341184122.511336</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2.369</t>
+          <t>-466038604.307249</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2.744</t>
+          <t>-521044646.263298</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2.863</t>
+          <t>-366332817.358527</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2.821</t>
+          <t>-483822657.499647</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.824</t>
+          <t>-393336886.669167</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>1890.2772402623</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>1839.33568824915</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>1930.84214536971</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>1970.11796552579</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2026.86804753876</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>1678.28185459926</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>1526.39746971163</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>1461.6812192318</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1456.65244250812</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1461.09452163681</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>1473.721052217</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.712</t>
+          <t>1483.04444225024</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1487.93226773825</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>1489.67781688423</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1488.51685217465</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>1648.1116457242</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1665.69437611392</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1760.8456248463</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1783.47790941441</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1854.88597569128</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>1567.86453576026</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>1435.00262682952</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>1387.83299476777</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>1387.00689975323</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>1389.37753430035</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>1397.1655681611</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>1403.08389195462</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>1406.30183568053</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>1407.55574027078</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>1407.39621365589</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>70146.6509908131</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>65685.4886289819</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>66834.3465453439</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>74436.676492476</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>86098.9122527962</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>100955.947780814</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>117693.969452568</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>132631.387957086</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>159727.706163</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>137472.431751158</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>183520.985987167</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>235217.897164638</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>225859.846749632</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>219713.705160467</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>210599.303925517</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>26737263544.1391</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>26955889601.0491</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>24740229491.6078</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>25582417095.7369</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>27118648236.3305</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>24927166509.2944</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>22371971106.3773</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>23037788043.5058</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>23975093828.5428</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>20570150648.1947</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>21432137171.19</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>23812818378.1709</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>24081103692.034</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>26105593597.537</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>29609892110.9002</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>49666.4642545321</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>49453.7174972708</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>51389.0746794389</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>54713.3696679328</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>71103.5119451207</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85524.9377299414</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>93890.6427929802</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>109956.498693934</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>145231.802819572</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>113826.77545276</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>157932.056653068</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>199795.74576211</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>214769.624788247</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>211524.186856103</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>203016.649097354</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>159660.176</t>
+          <t>9730088981.14262</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>165538.318</t>
+          <t>11044317844.2817</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>176488.77</t>
+          <t>12360374051.5573</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>185008.412</t>
+          <t>12775891578.8425</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>194145.927</t>
+          <t>14801486748.1818</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>166608.509</t>
+          <t>13958051583.1318</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>155857.243</t>
+          <t>15536828357.6791</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>157350.939</t>
+          <t>16031940415.0901</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>159747.607</t>
+          <t>17287474688.7175</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>162810.544</t>
+          <t>14674751031.863</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>169976.613</t>
+          <t>17438709717.0057</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>173429.409</t>
+          <t>22300126352.7337</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>190651.007</t>
+          <t>22794617869.0516</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>212782.301</t>
+          <t>22833443513.047</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>237573.657</t>
+          <t>22749148680.2251</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>68936.963</t>
+          <t>20480.186736281</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>74522.705</t>
+          <t>16231.7711317111</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78386.638</t>
+          <t>15445.271865905</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>77871.127</t>
+          <t>19723.3068245432</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>82806.33</t>
+          <t>14995.4003076755</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>72426.913</t>
+          <t>15431.0100508725</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>68493.533</t>
+          <t>23803.3266595883</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>68041.404</t>
+          <t>22674.8892631526</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>68774.789</t>
+          <t>14495.903343428</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>70833.183</t>
+          <t>23645.6562983981</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>76726.992</t>
+          <t>25588.9293340988</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>80070.701</t>
+          <t>35422.1514025275</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>89154.68</t>
+          <t>11090.221961385</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>99676.829</t>
+          <t>8189.51830436339</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>111104.239</t>
+          <t>7582.65482816289</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>162120.298</t>
+          <t>17007174562.9965</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>170025.762</t>
+          <t>15911571756.7674</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>182921.881</t>
+          <t>12379855440.0505</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>200682.613</t>
+          <t>12806525516.8944</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>199587.141</t>
+          <t>12317161488.1488</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>178754.606</t>
+          <t>10969114926.1626</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>176796.6</t>
+          <t>6835142748.69821</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>183240.95</t>
+          <t>7005847628.41572</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>187707.083</t>
+          <t>6687619139.82529</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>196664.375</t>
+          <t>5895399616.33168</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>200049.932</t>
+          <t>3993427454.18431</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>201148.805</t>
+          <t>1512692025.43721</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>218269.753</t>
+          <t>1286485822.98235</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>238073.602</t>
+          <t>3272150084.48998</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>262824.622</t>
+          <t>6860743430.67511</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>114147.225875649</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>110966.355629401</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>132241.744397382</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>156478.143012569</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.944</t>
+          <t>171963.54900074</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>193117.093305863</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>247232.239743633</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.286</t>
+          <t>292052.756952491</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.542</t>
+          <t>354329.380354619</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.424</t>
+          <t>372936.688848044</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.731</t>
+          <t>480425.001276</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2.916</t>
+          <t>574654.70986</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>3.083</t>
+          <t>588944.9846336</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>583216.29037712</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>3.727</t>
+          <t>563014.9626805</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>102743.677</t>
+          <t>0.0733779945744437</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>108059.503</t>
+          <t>0.0887033242857149</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>113953.796</t>
+          <t>0.100863249481233</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>120491.019</t>
+          <t>0.0933029598799284</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>121860.683</t>
+          <t>0.0867404118488087</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>110646.575</t>
+          <t>0.0993095661083255</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>103059.404</t>
+          <t>0.0971911769495896</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>105492.636</t>
+          <t>0.0985718081669021</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>106194.74</t>
+          <t>0.100116682433984</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>107549.058</t>
+          <t>0.0895312346592827</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>111631.333</t>
+          <t>0.0919295784435428</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>111397.13</t>
+          <t>0.0969211764304595</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>122658.224</t>
+          <t>0.0930105258683355</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>136706.249</t>
+          <t>0.0966429565658225</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>152326.11</t>
+          <t>0.0916909481501923</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>53326.5837553719</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>52222.90846428</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>64428.790986977</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.062</t>
+          <t>78557.935304634</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>87303.5822310153</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>96534.6268827779</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>123403.916032795</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>145496.806798059</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>171928.368796653</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>182407.24772453</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>237382.862769301</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>281371.725631559</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>289934.562725639</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>290335.076160917</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>284097.13937937</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>28611.632</t>
+          <t>90303.9866791231</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30545.224</t>
+          <t>84414.1067305556</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>31218.443</t>
+          <t>103484.588721022</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>36251.097</t>
+          <t>127918.836172003</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>37035.301</t>
+          <t>137447.982919183</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>34797.984</t>
+          <t>146397.051427448</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>33163.643</t>
+          <t>184091.784663292</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>34000.298</t>
+          <t>219820.902877605</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>33261.233</t>
+          <t>256591.455704771</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>36183.199</t>
+          <t>270168.420960388</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>37114.124</t>
+          <t>353759.979576064</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>37749.556</t>
+          <t>418100.537944051</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>40595.486</t>
+          <t>428966.473399493</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>43946.903</t>
+          <t>430197.169784549</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>48668.046</t>
+          <t>421707.261913733</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>140.94</t>
+          <t>550799.648698728</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>143.97</t>
+          <t>502771.859258796</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>151.09</t>
+          <t>582483.903597909</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>114.81</t>
+          <t>701723.91456149</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>123.59</t>
+          <t>786384.108109911</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>108.14</t>
+          <t>853145.516452215</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>106.53</t>
+          <t>1110204.13755865</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>100.12</t>
+          <t>1284168.71246861</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>106.77</t>
+          <t>1504807.37619439</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>1815886.33513375</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>106.73</t>
+          <t>2369022.40123853</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>112.11</t>
+          <t>2743962.45553503</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>2862778.3551911</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>126.81</t>
+          <t>2821318.31958435</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>128.29</t>
+          <t>2823587.58599551</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>18.817</t>
+          <t>247555.553224008</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>19.713</t>
+          <t>248730.832544665</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17.399</t>
+          <t>257787.541738712</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15.798</t>
+          <t>278817.325589052</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>14.892</t>
+          <t>288007.309718291</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>12.819</t>
+          <t>294450.191303344</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>9.779</t>
+          <t>307201.937511602</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>329313.648968784</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7.163</t>
+          <t>347630.910572949</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>6.995</t>
+          <t>361790.476322751</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>5.711</t>
+          <t>384744.121221175</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>4.964</t>
+          <t>412944.771778177</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5.241</t>
+          <t>436595.256299034</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>5.699</t>
+          <t>460197.836437337</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>6.388</t>
+          <t>485911.863432027</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>156374.98630053</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>163963.125423438</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>171754.292166337</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>180029.62988817</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>188611.220318274</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>198748.982455653</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>208676.920843556</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>221054.929686774</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>233645.767831333</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>243668.409182887</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>258174.090357084</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>277393.589634682</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>293488.888869237</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>309287.235238431</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>326393.448083422</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>87426.2058569907</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>87650.5125880129</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>106640.982279415</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>122233.10730004</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>136521.249994697</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>157550.613918541</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>201584.577644165</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>235368.673872272</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>281901.022413069</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>294240.077173523</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>381645.306761475</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>457558.37775307</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>469546.766084787</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>465322.97411669</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>447161.556235218</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>68936963000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>74522705000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>78386638000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>77871127000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>82806330000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>72426913000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>68493533000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>68041404000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>68774789000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>70833183000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>76726992000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>80070701000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>89154680000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>99676829000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>111104239000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>159660176212.213</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>165538317824.663</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>176488769880.351</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>185008412128.888</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>194145927287.217</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>166608508721.801</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>155857242502.896</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>157350939471.152</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>159747607028.538</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>162810543957.806</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>169976613195.317</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>173429409357.288</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>190651006689.069</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>212782301329.899</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>237573657268.388</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>102743676849.126</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>108059502815.42</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>113953796434.844</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>120491019446.615</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>121860682680.697</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>110646575372.814</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>103059403758.666</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>105492635634.461</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>106194740165.901</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>107549057962.187</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>111631332687.487</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>111397129577.328</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>122658224485.25</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>136706249484.089</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>152326109562.284</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>96874612</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>99380967</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>100229553</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>103734625</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>104667311</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>106264607</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>108611120</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>113378872</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>115174342</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>117182364</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>121658175</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>123605873</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>135569052</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>151171492</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>168803678</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>36469234</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40516098</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>40597124</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>39526124</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>40854327</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>43155393</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>44872672</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>46550098</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>47214275</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>48479535</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>52063443</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>53990763</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>59918507</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>66911669</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>74640901</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>159660176212.213</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>165538317824.663</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>176488769880.351</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>185008412128.888</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>194145927287.217</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>166608508721.801</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>155857242502.896</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>157350939471.152</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>159747607028.538</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>162810543957.806</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>169976613195.317</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>173429409357.288</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>190651006689.069</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>212782301329.899</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>237573657268.388</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>68936963000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>74522705000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>78386638000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>77871127000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>82806330000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>72426913000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>68493533000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>68041404000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>68774789000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>70833183000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>76726992000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>80070701000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>89154680000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>99676829000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>111104239000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>352659.977508832</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>343818.891039101</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>424059.334916915</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>503277.12338178</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>550006.490494811</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>602121.477731851</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>765627.015501197</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>898556.51322495</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1068647.62990199</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1119800.69253673</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1443519.27274689</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1711859.33158715</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1759671.71259452</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1752939.4422821</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1714343.06732921</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>177730.192743138</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>172064.619511674</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>210125.57295406</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>250151.943131748</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>273969.234653379</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>303947.666221749</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>385676.363477963</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>455189.576572602</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>538492.47596642</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>564408.497206022</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>735405.288394</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>875658.9162447</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>898513.2400055</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>895520.14240908</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>868868.8196628</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1564068.99089671</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1506780.42075888</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1481906.74443716</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1491725.47919542</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1552341.97240822</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1628484.84945432</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1751914.07833343</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1844834.46277905</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1979896.99864193</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2406311.64761134</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2576513.72541382</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2708886.94875541</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2897722.27171639</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>3006230.62813408</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>3247346.61183247</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
